--- a/data/comments.xlsx
+++ b/data/comments.xlsx
@@ -382,22 +382,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>depth</t>
+          <t>pers_exp</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>feeling</t>
+          <t>emot_exp</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>pol_opin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>breadth</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>pol_op</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
